--- a/dados/excel/genero_lideranca.xlsx
+++ b/dados/excel/genero_lideranca.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>13916</v>
+        <v>14469</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>10684</v>
+        <v>11182</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>76.77</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="3">
@@ -792,13 +792,13 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>1364</v>
+        <v>1356</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>62.24</v>
+        <v>62.02</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>12552</v>
+        <v>13113</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>9835</v>
+        <v>10341</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>78.34999999999999</v>
+        <v>78.86</v>
       </c>
     </row>
   </sheetData>
